--- a/data/products.xlsx
+++ b/data/products.xlsx
@@ -1,152 +1,49 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Products"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="34">
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>sku</t>
-  </si>
-  <si>
-    <t>price</t>
-  </si>
-  <si>
-    <t>stock</t>
-  </si>
-  <si>
-    <t>variant</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>category</t>
-  </si>
-  <si>
-    <t>Nails By Ayidaah Press-On Nail Set</t>
-  </si>
-  <si>
-    <t>NBA-PRESSON-24</t>
-  </si>
-  <si>
-    <t>Rs. 1,690</t>
-  </si>
-  <si>
-    <t>Check availability</t>
-  </si>
-  <si>
-    <t>French Manicure; 24 pcs with glue stickers</t>
-  </si>
-  <si>
-    <t>False nail set with cute pattern designs, glue stickers, full cover fit, and water-resistant nail art positioning. Seeded from public Daraz listing sold by Ayidaah Beauty LK.</t>
-  </si>
-  <si>
-    <t>Press-on nails</t>
-  </si>
-  <si>
-    <t>Custom Press-On Nail Set</t>
-  </si>
-  <si>
-    <t>NBA-CUSTOM</t>
-  </si>
-  <si>
-    <t>Quote after design</t>
-  </si>
-  <si>
-    <t>Made to order</t>
-  </si>
-  <si>
-    <t>Custom length, shape, and design</t>
-  </si>
-  <si>
-    <t>Custom stick-on nails for customers who want a specific design, shade, or occasion set. Confirm final design and price with manager.</t>
-  </si>
-  <si>
-    <t>Custom nails</t>
-  </si>
-  <si>
-    <t>Classic Nude Press-On Set</t>
-  </si>
-  <si>
-    <t>NBA-NUDE</t>
-  </si>
-  <si>
-    <t>Confirm with store</t>
-  </si>
-  <si>
-    <t>Neutral everyday style</t>
-  </si>
-  <si>
-    <t>Simple neutral press-on nails suitable for work, events, and daily wear. Starter catalog item; update with actual shades and pricing.</t>
-  </si>
-  <si>
-    <t>French Tip Press-On Set</t>
-  </si>
-  <si>
-    <t>NBA-FRENCH</t>
-  </si>
-  <si>
-    <t>French tip style</t>
-  </si>
-  <si>
-    <t>Classic French tip press-on nails for clean, polished looks. Starter catalog item; update with actual pricing and photos later.</t>
-  </si>
-  <si>
-    <t>Event / Bridal Press-On Set</t>
-  </si>
-  <si>
-    <t>NBA-EVENT</t>
-  </si>
-  <si>
-    <t>Occasion and bridal designs</t>
-  </si>
-  <si>
-    <t>Premium occasion nails for weddings, shoots, parties, or events. Ask customer for date, outfit color, preferred length, and reference design.</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFffffff"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color rgb="FFffffff"/>
+      <sz val="11"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -154,6 +51,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1f4e78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
   </fills>
@@ -189,49 +91,123 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G6" displayName="ProductsTable" name="ProductsTable" id="1" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ProductsTable" displayName="ProductsTable" ref="A1:J6" headerRowCount="1" totalsRowShown="0">
   <autoFilter ref="A1:G6"/>
   <tableColumns count="7">
-    <tableColumn name="name" id="1"/>
-    <tableColumn name="sku" id="2"/>
-    <tableColumn name="price" id="3"/>
-    <tableColumn name="stock" id="4"/>
-    <tableColumn name="variant" id="5"/>
-    <tableColumn name="description" id="6"/>
-    <tableColumn name="category" id="7"/>
+    <tableColumn id="1" name="name"/>
+    <tableColumn id="2" name="sku"/>
+    <tableColumn id="3" name="price"/>
+    <tableColumn id="4" name="stock"/>
+    <tableColumn id="5" name="variant"/>
+    <tableColumn id="6" name="description"/>
+    <tableColumn id="7" name="category"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showColumnStripes="0" showRowStripes="1" showLastColumn="0" showFirstColumn="0"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -519,164 +495,310 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" style="4" width="34.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="4" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="4" width="20.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="4" width="20.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="4" width="28.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="4" width="90.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="4" width="20.005" customWidth="1" bestFit="1"/>
+    <col width="34" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
+    <col width="18" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
+    <col width="20" bestFit="1" customWidth="1" style="4" min="3" max="3"/>
+    <col width="20" bestFit="1" customWidth="1" style="4" min="4" max="4"/>
+    <col width="28" bestFit="1" customWidth="1" style="4" min="5" max="5"/>
+    <col width="90" bestFit="1" customWidth="1" style="4" min="6" max="6"/>
+    <col width="20" bestFit="1" customWidth="1" style="4" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
+    <col width="70" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="17.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
+    <row r="1" ht="17.25" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>sku</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>stock</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>variant</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="H1" s="6" t="inlineStr">
+        <is>
+          <t>image_url</t>
+        </is>
+      </c>
+      <c r="I1" s="6" t="inlineStr">
+        <is>
+          <t>product_url</t>
+        </is>
+      </c>
+      <c r="J1" s="6" t="inlineStr">
+        <is>
+          <t>image_source</t>
+        </is>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="28.5" customFormat="1" s="2">
-      <c r="A2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>13</v>
+    <row r="2" ht="28.5" customFormat="1" customHeight="1" s="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Nails By Ayidaah Press-On Nail Set</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>NBA-PRESSON-24</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>Rs. 1,690</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>Check availability</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>French Manicure; 24 pcs with glue stickers</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>False nail set with cute pattern designs, glue stickers, full cover fit, and water-resistant nail art positioning. Seeded from public Daraz listing sold by Ayidaah Beauty LK.</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>Press-on nails</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>https://img.drz.lazcdn.com/static/lk/p/ee1cbfc0408a94db851ba95af3666164.jpg</t>
+        </is>
+      </c>
+      <c r="I2" s="8" t="inlineStr">
+        <is>
+          <t>https://www.daraz.lk/products/nails-by-ayidaah-with-24pcs-glue-stickers-cute-pattern-false-nails-with-design-press-on-nails-artificial-nails-full-cover-water-proof-nail-art-i287547453.html</t>
+        </is>
+      </c>
+      <c r="J2" s="8" t="inlineStr">
+        <is>
+          <t>Daraz listing sold by Ayidaah Beauty LK</t>
+        </is>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="28.5" customFormat="1" s="2">
-      <c r="A3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>20</v>
+    <row r="3" ht="28.5" customFormat="1" customHeight="1" s="2">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Custom Press-On Nail Set</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>NBA-CUSTOM</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Quote after design</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>Made to order</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>Custom length, shape, and design</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>Custom stick-on nails for customers who want a specific design, shade, or occasion set. Confirm final design and price with manager.</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Custom nails</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="n"/>
+      <c r="I3" s="8" t="n"/>
+      <c r="J3" s="8" t="inlineStr">
+        <is>
+          <t>No verified Nails by Ayidaah image yet</t>
+        </is>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="28.5" customFormat="1" s="2">
-      <c r="A4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>13</v>
+    <row r="4" ht="28.5" customFormat="1" customHeight="1" s="2">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Classic Nude Press-On Set</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>NBA-NUDE</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Confirm with store</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Check availability</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Neutral everyday style</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Simple neutral press-on nails suitable for work, events, and daily wear. Starter catalog item; update with actual shades and pricing.</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>Press-on nails</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="n"/>
+      <c r="I4" s="8" t="n"/>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>No verified Nails by Ayidaah image yet</t>
+        </is>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="28.5" customFormat="1" s="2">
-      <c r="A5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>13</v>
+    <row r="5" ht="28.5" customFormat="1" customHeight="1" s="2">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>French Tip Press-On Set</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>NBA-FRENCH</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Confirm with store</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Check availability</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>French tip style</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Classic French tip press-on nails for clean, polished looks. Starter catalog item; update with actual pricing and photos later.</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Press-on nails</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="n"/>
+      <c r="I5" s="8" t="n"/>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>No verified Nails by Ayidaah image yet</t>
+        </is>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="28.5" customFormat="1" s="2">
-      <c r="A6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>20</v>
+    <row r="6" ht="28.5" customFormat="1" customHeight="1" s="2">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Event / Bridal Press-On Set</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>NBA-EVENT</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Quote after design</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Made to order</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Occasion and bridal designs</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>Premium occasion nails for weddings, shoots, parties, or events. Ask customer for date, outfit color, preferred length, and reference design.</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Custom nails</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="n"/>
+      <c r="I6" s="8" t="n"/>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>No verified Nails by Ayidaah image yet</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>